--- a/pensum/ma07/MA07_Pris_Regneark_Pris.xlsx
+++ b/pensum/ma07/MA07_Pris_Regneark_Pris.xlsx
@@ -1223,7 +1223,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1390,6 +1390,14 @@
     </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1781,7 +1789,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="32.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
         <v>20</v>
       </c>
@@ -2058,11 +2066,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="30" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c s="42" r="B30" t="s">
         <v>68</v>
       </c>
       <c r="C30" s="20" t="s">
@@ -2118,11 +2126,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c s="43" r="B37" t="s">
         <v>81</v>
       </c>
       <c r="C37" s="20" t="s">
@@ -2239,8 +2247,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row ht="27" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A6" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="25" t="n">
@@ -2263,8 +2271,8 @@
         <v>800</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+    <row ht="27" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A9" t="s">
         <v>102</v>
       </c>
       <c r="B9" s="25" t="n">
@@ -3062,7 +3070,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
         <v>183</v>
       </c>
@@ -3413,8 +3421,8 @@
         <v>640</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A7" t="s">
         <v>207</v>
       </c>
       <c r="B7" s="41" t="n">
@@ -3887,8 +3895,8 @@
         <v>257</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+    <row ht="27" customHeight="true" r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A21" t="s">
         <v>258</v>
       </c>
       <c r="B21" s="24" t="n">
@@ -4142,11 +4150,11 @@
         <v>292</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="58" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c s="42" r="B58" t="s">
         <v>219</v>
       </c>
       <c r="C58" s="38" t="n">
@@ -4160,11 +4168,11 @@
         <v>294</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="59" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c s="42" r="B59" t="s">
         <v>296</v>
       </c>
       <c r="C59" s="38" t="n">
@@ -4178,11 +4186,11 @@
         <v>297</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="60" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c s="42" r="B60" t="s">
         <v>296</v>
       </c>
       <c r="C60" s="38" t="n">
@@ -4196,11 +4204,11 @@
         <v>299</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="61" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c s="42" r="B61" t="s">
         <v>301</v>
       </c>
       <c r="C61" s="38" t="n">
